--- a/Multi_library_df_test8.xlsx
+++ b/Multi_library_df_test8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\st212\Documents\GitHub\job_description_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B9202C-4BA3-42B9-88D1-A6AAD0069ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1769745A-4E3B-4117-B9D7-7A604E573217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -427,6 +427,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -792,12 +793,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="88.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="38.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="88.44140625" style="3"/>
+    <col min="2" max="4" width="38.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -814,7 +815,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -831,7 +832,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -848,7 +849,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -865,7 +866,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -882,7 +883,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -899,7 +900,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -916,7 +917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
